--- a/Assignments/Final-Exam/Busters Burritos.xlsx
+++ b/Assignments/Final-Exam/Busters Burritos.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="D14">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -673,18 +673,18 @@
         </is>
       </c>
       <c r="D16">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -693,18 +693,18 @@
         </is>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -713,18 +713,18 @@
         </is>
       </c>
       <c r="D18">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -733,18 +733,18 @@
         </is>
       </c>
       <c r="D19">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -753,18 +753,18 @@
         </is>
       </c>
       <c r="D20">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -773,18 +773,18 @@
         </is>
       </c>
       <c r="D21">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -793,18 +793,18 @@
         </is>
       </c>
       <c r="D22">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -813,18 +813,18 @@
         </is>
       </c>
       <c r="D23">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -833,18 +833,18 @@
         </is>
       </c>
       <c r="D24">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -853,18 +853,18 @@
         </is>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -884,7 +884,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="28">
@@ -904,7 +904,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -924,7 +924,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="30">
@@ -944,7 +944,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="31">
@@ -964,7 +964,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Mild</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="D31">
-        <v>4.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -984,16 +984,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D32">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="33">
@@ -1004,16 +1004,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D33">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="34">
@@ -1024,16 +1024,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D34">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="35">
@@ -1044,16 +1044,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D35">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="36">
@@ -1064,222 +1064,222 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D36">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D37">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D38">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D39">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D40">
-        <v>6.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D41">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D42">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D43">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D44">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D45">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D46">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D47">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1309,17 +1309,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D48">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D49">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D50">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Sausage</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D51">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D52">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D53">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D54">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D55">
-        <v>6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D56">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="57">
@@ -1489,11 +1489,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D57">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -1509,11 +1509,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D58">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="59">
@@ -1529,11 +1529,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D59">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="60">
@@ -1549,11 +1549,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D60">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="61">
@@ -1569,11 +1569,1211 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D61">
-        <v>6</v>
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D65">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D78">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D79">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D80">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D81">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D82">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D83">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D84">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D85">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D89">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D90">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D91">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D93">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D94">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D95">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D97">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D98">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D99">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D100">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D101">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D102">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D103">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D104">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D105">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D106">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D107">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D108">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D109">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D110">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sausage</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D111">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D112">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D113">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D114">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D115">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D116">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D117">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D118">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D119">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D120">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Chorizo</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D121">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
